--- a/sampleprojects/TaxReturn/excel/states/VT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/VT.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $14,850 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,500 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Default (Single/MFS): $7,400 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/VT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/VT.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail; set result.vt_military_retirement_exemption = 0.0; if result.state_calc_total_agi &lt;= vt_military_agi_full_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income; } else { if result.state_calc_total_agi &lt; vt_military_agi_no_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income * ((the floor of ((vt_military_agi_no_exemption_threshold - result.state_calc_total_agi) / (vt_military_agi_no_exemption_threshold - vt_military_agi_full_exemption_threshold) * 100.0 + 0.5)) / 100.0); } endif } endif; add "  VT Schedule IN-112 line 13 military retirement income exemption: $" + result.vt_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $14,850 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,500 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Default (Single/MFS): $7,400 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -257,7 +257,7 @@
     <t>125000.0</t>
   </si>
   <si>
-    <t>VT AGI threshold for full military retirement exemption (2025). Source: MOAA</t>
+    <t>Vermont military retirement income exemption, Act 71 of 2025 (32 V.S.A. 5830e(d)): all federally taxable military retirement and survivor benefit income is exempt when federal AGI is $125,000 or less, any filing status (Schedule IN-112 Part I line 13; 2025 IN-112 instructions p. 3-4).</t>
   </si>
   <si>
     <t>vt_military_agi_no_exemption_threshold</t>
@@ -266,7 +266,7 @@
     <t>175000.0</t>
   </si>
   <si>
-    <t>VT AGI threshold above which no military retirement exemption (2025). Source: MOAA</t>
+    <t>Vermont military retirement income exemption phases out between federal AGI $125,000 and $175,000: the exempt share is (175,000 - AGI) / 50,000 rounded to two decimals, and nothing is exempt at $175,000 or more (IN-112 Military Retirement Income Exemption Worksheet Section II; 32 V.S.A. 5830e(d)).</t>
   </si>
   <si>
     <t>vt_military_retirement_exemption</t>
@@ -275,7 +275,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>VT military retirement exemption amount (computed based on AGI)</t>
+    <t>VT military retirement income exemption (computed per return in VT_Tax): the pay times the Section II share, 1.00 at or below $125,000 of federal AGI (#1330).</t>
   </si>
   <si>
     <t>vt_military_retirement_taxable</t>

--- a/sampleprojects/TaxReturn/excel/states/VT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/VT.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail; set result.vt_military_retirement_exemption = 0.0; if result.state_calc_total_agi &lt;= vt_military_agi_full_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income; } else { if result.state_calc_total_agi &lt; vt_military_agi_no_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income * ((the floor of ((vt_military_agi_no_exemption_threshold - result.state_calc_total_agi) / (vt_military_agi_no_exemption_threshold - vt_military_agi_full_exemption_threshold) * 100.0 + 0.5)) / 100.0); } endif } endif; add "  VT Schedule IN-112 line 13 military retirement income exemption: $" + result.vt_military_retirement_exemption to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail; set result.vt_military_retirement_exemption = 0.0; if result.state_calc_resident_status is equal to "full_year" then { if result.state_calc_total_agi &lt;= vt_military_agi_full_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income; } else { if result.state_calc_total_agi &lt; vt_military_agi_no_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income * ((the floor of ((vt_military_agi_no_exemption_threshold - result.state_calc_total_agi) / (vt_military_agi_no_exemption_threshold - vt_military_agi_full_exemption_threshold) * 100.0 + 0.5)) / 100.0); } endif } endif } endif; add "  VT Schedule IN-112 line 13 military retirement income exemption: $" + result.vt_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>

--- a/sampleprojects/TaxReturn/excel/states/VT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/VT.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Vermont Tax Calculation (top marginal 8.75%)" to job.audit_trail; set result.vt_military_retirement_exemption = 0.0; if result.state_calc_resident_status is equal to "full_year" then { if result.state_calc_total_agi &lt;= vt_military_agi_full_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income; } else { if result.state_calc_total_agi &lt; vt_military_agi_no_exemption_threshold then { set result.vt_military_retirement_exemption = result.military_retirement_income * ((the floor of ((vt_military_agi_no_exemption_threshold - result.state_calc_total_agi) / (vt_military_agi_no_exemption_threshold - vt_military_agi_full_exemption_threshold) * 100.0 + 0.5)) / 100.0); } endif } endif } endif; add "  VT Schedule IN-112 line 13 military retirement income exemption: $" + result.vt_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $14,850 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 14850.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,500 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 11500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Default (Single/MFS): $7,400 std ded, 8.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.vt_military_retirement_exemption - 7400.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0875</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -257,7 +257,7 @@
     <t>125000.0</t>
   </si>
   <si>
-    <t>VT AGI threshold for full military retirement exemption (2025). Source: MOAA</t>
+    <t>Vermont military retirement income exemption, Act 71 of 2025 (32 V.S.A. 5830e(d)): all federally taxable military retirement and survivor benefit income is exempt when federal AGI is $125,000 or less, any filing status (Schedule IN-112 Part I line 13; 2025 IN-112 instructions p. 3-4).</t>
   </si>
   <si>
     <t>vt_military_agi_no_exemption_threshold</t>
@@ -266,7 +266,7 @@
     <t>175000.0</t>
   </si>
   <si>
-    <t>VT AGI threshold above which no military retirement exemption (2025). Source: MOAA</t>
+    <t>Vermont military retirement income exemption phases out between federal AGI $125,000 and $175,000: the exempt share is (175,000 - AGI) / 50,000 rounded to two decimals, and nothing is exempt at $175,000 or more (IN-112 Military Retirement Income Exemption Worksheet Section II; 32 V.S.A. 5830e(d)).</t>
   </si>
   <si>
     <t>vt_military_retirement_exemption</t>
@@ -275,7 +275,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>VT military retirement exemption amount (computed based on AGI)</t>
+    <t>VT military retirement income exemption (computed per return in VT_Tax): the pay times the Section II share, 1.00 at or below $125,000 of federal AGI (#1330).</t>
   </si>
   <si>
     <t>vt_military_retirement_taxable</t>
